--- a/data/trans_camb/P38C-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Estudios-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,01</t>
+          <t>-2,72; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,75</t>
+          <t>-2,97; 2,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,74</t>
+          <t>-1,84; 2,76</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,61</t>
+          <t>-3,02; 4,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,96</t>
+          <t>-3,16; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,08</t>
+          <t>-1,97; 3,06</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -1,25</t>
+          <t>-32,02; -0,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 1,98</t>
+          <t>-11,55; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -0,71</t>
+          <t>-20,81; -0,62</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -1,64</t>
+          <t>-40,08; -0,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 2,33</t>
+          <t>-13,6; 2,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -0,85</t>
+          <t>-25,17; -0,75</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 7,46</t>
+          <t>-3,69; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,71</t>
+          <t>1,22; 9,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,09</t>
+          <t>0,1; 6,97</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,39</t>
+          <t>-4,46; 9,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,97</t>
+          <t>1,5; 11,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,85</t>
+          <t>0,14; 8,67</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -0,36</t>
+          <t>-22,89; -0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 1,65</t>
+          <t>-6,94; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -0,05</t>
+          <t>-13,53; -0,15</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,81; -0,45</t>
+          <t>-28,22; -0,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 1,88</t>
+          <t>-7,96; 1,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -0,06</t>
+          <t>-16,01; -0,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38C-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>-0,13</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,27</t>
+          <t>-5,64; 2,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,58</t>
+          <t>-1,48; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,76</t>
+          <t>-2,15; 1,91</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>-1,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>-0,14%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,84</t>
+          <t>-6,26; 2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,79</t>
+          <t>-1,57; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,06</t>
+          <t>-2,34; 2,11</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-10,02</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-2,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-2,89</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,02; -0,58</t>
+          <t>-5,75; -0,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 2,04</t>
+          <t>-4,96; -0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -0,62</t>
+          <t>-4,85; -1,08</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-12,65%</t>
+          <t>-3,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-2,99%</t>
+          <t>-3,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,68%</t>
+          <t>-3,5%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -0,67</t>
+          <t>-7,21; -0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 2,35</t>
+          <t>-5,69; -0,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -0,75</t>
+          <t>-5,79; -1,3</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,13</t>
+          <t>-2,2; 7,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,41</t>
+          <t>1,82; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,97</t>
+          <t>1,5; 7,53</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 9,15</t>
+          <t>-2,63; 10,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 11,89</t>
+          <t>2,12; 11,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 8,67</t>
+          <t>1,76; 9,36</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-6,8</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-1,45</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -0,36</t>
+          <t>-4,44; 0,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,24</t>
+          <t>-2,35; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -0,15</t>
+          <t>-2,83; -0,23</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-8,35%</t>
+          <t>-2,53%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-1,29%</t>
+          <t>-1,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,59%</t>
+          <t>-1,72%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,22; -0,43</t>
+          <t>-5,42; 0,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,44</t>
+          <t>-2,66; 0,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -0,16</t>
+          <t>-3,32; -0,28</t>
         </is>
       </c>
     </row>
